--- a/AfterToken/Configs/GameConfig/Datas/item.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,7 +813,6 @@
       <c r="I8" t="b">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Material</t>
@@ -856,7 +855,6 @@
       <c r="I9" t="b">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Material</t>
@@ -899,7 +897,6 @@
       <c r="I10" t="b">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Material</t>
@@ -942,7 +939,6 @@
       <c r="I11" t="b">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Material</t>
@@ -985,7 +981,6 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Consumable</t>
@@ -998,6 +993,117 @@
       </c>
       <c r="M12" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>11001</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Enhancement Part</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Basic material for skill upgrades.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11002</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tactical Core</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Advanced material for skill upgrades.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11003</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Gene Sample</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rare material for skill upgrades.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>400</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/AfterToken/Configs/GameConfig/Datas/item.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,16 @@
           <t>stackLimit</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>affinityValue</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>companionAccept</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +559,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,6 +634,16 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>堆叠上限</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>好感值(0=不可赠送)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1=NPC接受赠送 0=拒收</t>
         </is>
       </c>
     </row>
@@ -658,6 +688,12 @@
       <c r="M4" t="n">
         <v>99</v>
       </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -700,6 +736,12 @@
       <c r="M5" t="n">
         <v>99</v>
       </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -742,6 +784,12 @@
       <c r="M6" t="n">
         <v>50</v>
       </c>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -784,6 +832,12 @@
       <c r="M7" t="n">
         <v>10</v>
       </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -826,6 +880,12 @@
       <c r="M8" t="n">
         <v>99</v>
       </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -868,6 +928,12 @@
       <c r="M9" t="n">
         <v>99</v>
       </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -910,6 +976,12 @@
       <c r="M10" t="n">
         <v>99</v>
       </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -952,6 +1024,12 @@
       <c r="M11" t="n">
         <v>99</v>
       </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -994,6 +1072,12 @@
       <c r="M12" t="n">
         <v>10</v>
       </c>
+      <c r="N12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -1031,6 +1115,12 @@
       <c r="M13" t="n">
         <v>99</v>
       </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
@@ -1068,6 +1158,12 @@
       <c r="M14" t="n">
         <v>50</v>
       </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
@@ -1104,6 +1200,12 @@
       </c>
       <c r="M15" t="n">
         <v>20</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
